--- a/arabic_english_codeswitching_700_new.xlsx
+++ b/arabic_english_codeswitching_700_new.xlsx
@@ -536,7 +536,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط Colours، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Colours، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت donut وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت donut وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت chocolate lava cake وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت chocolate lava cake وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط Avenues، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Avenues، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت tiramisu وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت tiramisu وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>أهدوني شنطة Chanel في عيد ميلادي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
+          <t>أهدوني شنطة Chanel في تخرجي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>أهدوني شنطة Gucci في عيد ميلادي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
+          <t>أهدوني شنطة Gucci في تخرجي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -6078,7 +6078,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت ice cream sundae وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت ice cream sundae وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت brownie وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت brownie وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
@@ -6435,7 +6435,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط Uptown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Uptown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -6724,7 +6724,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط Boulevard World، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Boulevard World، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط Downtown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Downtown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت bubble tea وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت bubble tea وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
@@ -9291,7 +9291,7 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت chai latte وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت chai latte وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -9325,7 +9325,7 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>أهدوني ساعة Rolex في عيد ميلادي وكانت هدية فخمة، ولين الحين أحافظ عليها مثل الذهب.</t>
+          <t>أهدوني ساعة Rolex في تخرجي وكانت هدية فخمة، ولين الحين أحافظ عليها مثل الذهب.</t>
         </is>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -9376,7 +9376,7 @@
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>أهدوني شنطة Louis Vuitton في عيد ميلادي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
+          <t>أهدوني شنطة Louis Vuitton في تخرجي وكانت هدية فخمة، ما توقعت حد يهديني شي بهالمستوى.</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بعيد ميلادها في مطعم وسط KAFD، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط KAFD، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -11824,7 +11824,7 @@
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
         <is>
-          <t>في عيد ميلادي طلبت hotdog وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
+          <t>في تخرجي طلبت hotdog وكيكة من نفس المطعم لأنهم أفضل مكان جربته بصراحة.</t>
         </is>
       </c>
       <c r="B671" s="3" t="inlineStr">

--- a/arabic_english_codeswitching_700_new.xlsx
+++ b/arabic_english_codeswitching_700_new.xlsx
@@ -536,7 +536,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط Colours، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Colours ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>أختي ما تشتري مكياج إلا من MAC، وتقول الجودة تفرق عن أي ماركة ثانية.</t>
+          <t>أختي ما تشتري مكياج إلا من MAC ، وتقول الجودة تفرق عن أي ماركة ثانية.</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في T4 وأنا في Tim Hortons، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في T4 وأنا في Tim Hortons ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>كان عندي appraisal وبعده على طول budget، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
+          <t>كان عندي appraisal وبعده على طول budget ، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1250,7 +1250,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Kart N Go، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Kart N Go ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>كان عندي meeting وبعده على طول teamwork، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
+          <t>كان عندي meeting وبعده على طول teamwork ، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>نزّلت sequel وبعدها series، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت sequel وبعدها series ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Sudra Tea، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Sudra Tea ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط Avenues، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Avenues ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>أختي ما تشتري مكياج إلا من Sephora، وتقول الجودة تفرق عن أي ماركة ثانية.</t>
+          <t>أختي ما تشتري مكياج إلا من Sephora ، وتقول الجودة تفرق عن أي ماركة ثانية.</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Starbucks، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Starbucks ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>شاركت في تحدي cycling مع صحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
+          <t>شاركت في تحدي cycling مع أصحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>شفت HBO الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت HBO الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>شاركت في تحدي running مع صحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
+          <t>شاركت في تحدي running مع أصحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>نزّلت HBO وبعدها soundtrack، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت HBO وبعدها soundtrack ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>الفطور كان فيه ice cream sundae والعشاء steak، يوم أكل كامل ما نسيته بسهولة.</t>
+          <t>الفطور كان فيه ice cream sundae والعشاء steak ، يوم أكل كامل ما نسيته بسهولة.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Ole، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Ole ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>نزّلت rom-com وبعدها season finale، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت rom-com وبعدها season finale ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>شفت Shahid VIP الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت Shahid VIP الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>الفطور كان فيه pasta والعشاء mac&amp;cheese، يوم أكل كامل ما نسيته بسهولة.</t>
+          <t>الفطور كان فيه pasta والعشاء mac&amp;cheese ، يوم أكل كامل ما نسيته بسهولة.</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في Lagate وأنا في City Fresh Kitchen، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في Lagate وأنا في City Fresh Kitchen ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Costa، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Costa ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>الفطور كان فيه bagel والعشاء iced coffee، يوم أكل كامل ما نسيته بسهولة.</t>
+          <t>الفطور كان فيه bagel والعشاء iced coffee ، يوم أكل كامل ما نسيته بسهولة.</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
@@ -6435,7 +6435,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط Uptown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Uptown ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>شفت YouTube الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت YouTube الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>شفت prequel الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت prequel الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
@@ -6724,7 +6724,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط Boulevard World، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Boulevard World ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
@@ -6809,7 +6809,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>شاركت في تحدي taekwondo مع صحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
+          <t>شاركت في تحدي taekwondo مع أصحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -7200,7 +7200,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>الفطور كان فيه hot chocolate والعشاء cupcake، يوم أكل كامل ما نسيته بسهولة.</t>
+          <t>الفطور كان فيه hot chocolate والعشاء cupcake ، يوم أكل كامل ما نسيته بسهولة.</t>
         </is>
       </c>
       <c r="B399" s="3" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط Downtown، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط Downtown ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في Lagate وأنا في Claro، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في Lagate وأنا في Claro ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
@@ -8220,7 +8220,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في Costa وأنا في Tim Hortons، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في Costa وأنا في Tim Hortons ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
@@ -8492,7 +8492,7 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>الفطور كان فيه bubble tea والعشاء burrito، يوم أكل كامل ما نسيته بسهولة.</t>
+          <t>الفطور كان فيه bubble tea والعشاء burrito ، يوم أكل كامل ما نسيته بسهولة.</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
@@ -9053,7 +9053,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>نزّلت trailer وبعدها Spotify، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت trailer وبعدها Spotify ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>نزّلت Marvel وبعدها series، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت Marvel وبعدها series ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B535" s="3" t="inlineStr">
@@ -9835,7 +9835,7 @@
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>شفت league حماسي أمس وانبسطت مرة، وقعدت أتكلم عنه مع صحابي طول اليوم.</t>
+          <t>شفت league حماسي أمس وانبسطت مرة، وقعدت أتكلم عنه مع أصحابي طول اليوم.</t>
         </is>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>شفت premiere الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت premiere الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>احتفلنا بتخرجها في مطعم وسط KAFD، وكانت الأمسية من أحلى الليالي هالسنة.</t>
+          <t>احتفلنا بتخرجها في مطعم وسط KAFD ، وكانت الأمسية من أحلى الليالي هالسنة.</t>
         </is>
       </c>
       <c r="B577" s="3" t="inlineStr">
@@ -10311,7 +10311,7 @@
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في T7 وأنا في Sudra Tea، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في T7 وأنا في Sudra Tea ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>شاركت في تحدي judo مع صحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
+          <t>شاركت في تحدي judo مع أصحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
         </is>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>زميلي مكتبه في 66 Cups وأنا في A5، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
+          <t>زميلي مكتبه في 66 Cups وأنا في A5 ، فنتقابل بس وقت الغدا لأن المسافة بينا بعيدة شوي.</t>
         </is>
       </c>
       <c r="B597" s="3" t="inlineStr">
@@ -10634,7 +10634,7 @@
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>انصدمت من plot twist في الفيلم ولا توقعته أبدًا، وضليت أتكلم عنه مع صحابي كل الأسبوع.</t>
+          <t>انصدمت من plot twist في الفيلم ولا توقعته أبدًا، وقعدت أتكلم عنه مع أصحابي كل الأسبوع.</t>
         </is>
       </c>
       <c r="B601" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>كان عندي networking وبعده على طول invoice، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
+          <t>كان عندي networking وبعده على طول invoice ، يوم مرهق ما توقعت أخلصه بهالسرعة.</t>
         </is>
       </c>
       <c r="B625" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>نزّلت episode وبعدها animation، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
+          <t>نزّلت episode وبعدها animation ، قعدة سهر كاملة ما ندمت عليها أبدًا.</t>
         </is>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -11127,7 +11127,7 @@
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>شفت animation الجديد وصدمت من نهايته، وضليت أفكر فيه لين ثاني يوم.</t>
+          <t>شفت animation الجديد وصدمت من نهايته، وقعدت أفكر فيه لين ثاني يوم.</t>
         </is>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في City Fresh Kitchen، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في City Fresh Kitchen ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B659" s="3" t="inlineStr">
@@ -11994,7 +11994,7 @@
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
         <is>
-          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Chok، وقعدنا نضحك على مواقف الأسبوع.</t>
+          <t>احنا سوينا استراحة قصيرة وطلعنا نتغدى في Chok ، وقعدنا نضحك على مواقف الأسبوع.</t>
         </is>
       </c>
       <c r="B681" s="3" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
         <is>
-          <t>شاركت في تحدي boxing مع صحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
+          <t>شاركت في تحدي boxing مع أصحابي هالشهر، وكنا نتنافس على مين يلتزم أكثر.</t>
         </is>
       </c>
       <c r="B696" s="3" t="inlineStr">
